--- a/public/downloads/templates/new-client-onboarding-checklist-template.xlsx
+++ b/public/downloads/templates/new-client-onboarding-checklist-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="How to use" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Onboarding Checklist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Onboarding Checklist" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,11 +95,55 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,6 +159,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -528,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -563,8 +610,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Project Amazon PH Academy — Download Center</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -631,10 +693,10 @@
           <t>Phase 1 — Access &amp; Account Setup</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -717,10 +779,10 @@
           <t>Phase 2 — Account Audit</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -803,10 +865,10 @@
           <t>Phase 3 — Goals &amp; Strategy Alignment</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -874,10 +936,10 @@
           <t>Phase 4 — Campaign Setup / Cleanup</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -945,10 +1007,10 @@
           <t>Phase 5 — First Report &amp; Handoff</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1022,5 +1084,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>